--- a/0-assets/raw_data/main/3b-age-grouping/age_generation_quarterly_statistics.xlsx
+++ b/0-assets/raw_data/main/3b-age-grouping/age_generation_quarterly_statistics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Quarterly counts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Run info" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly counts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run info" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -461,7 +461,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -483,7 +483,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -505,10 +505,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -527,10 +527,10 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -549,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -571,10 +571,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -593,10 +593,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -615,13 +615,13 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
         <v>31</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -640,10 +640,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -684,10 +684,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="F12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -706,10 +706,10 @@
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>750</v>
+        <v>702</v>
       </c>
       <c r="F13" t="n">
-        <v>36</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14">
@@ -725,13 +725,13 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>879</v>
+        <v>808</v>
       </c>
       <c r="F14" t="n">
-        <v>124</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15">
@@ -747,13 +747,13 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>1055</v>
+        <v>973</v>
       </c>
       <c r="F15" t="n">
-        <v>176</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16">
@@ -769,13 +769,13 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" t="n">
-        <v>3002</v>
+        <v>2666</v>
       </c>
       <c r="F16" t="n">
-        <v>622</v>
+        <v>957</v>
       </c>
     </row>
     <row r="17">
@@ -791,13 +791,13 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>4907</v>
+        <v>4203</v>
       </c>
       <c r="F17" t="n">
-        <v>963</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="18">
@@ -813,13 +813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E18" t="n">
-        <v>3792</v>
+        <v>3754</v>
       </c>
       <c r="F18" t="n">
-        <v>1928</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="19">
@@ -835,13 +835,13 @@
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E19" t="n">
-        <v>2833</v>
+        <v>2630</v>
       </c>
       <c r="F19" t="n">
-        <v>1745</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="20">
@@ -854,16 +854,16 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E20" t="n">
-        <v>2535</v>
+        <v>2147</v>
       </c>
       <c r="F20" t="n">
-        <v>1953</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="21">
@@ -879,13 +879,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E21" t="n">
-        <v>1269</v>
+        <v>1119</v>
       </c>
       <c r="F21" t="n">
-        <v>1405</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="22">
@@ -901,13 +901,13 @@
         <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E22" t="n">
-        <v>789</v>
+        <v>994</v>
       </c>
       <c r="F22" t="n">
-        <v>1937</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="23">
@@ -923,13 +923,13 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E23" t="n">
-        <v>669</v>
+        <v>765</v>
       </c>
       <c r="F23" t="n">
-        <v>1407</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="24">
@@ -945,13 +945,13 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E24" t="n">
-        <v>636</v>
+        <v>657</v>
       </c>
       <c r="F24" t="n">
-        <v>1413</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="25">
@@ -967,13 +967,13 @@
         <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E25" t="n">
-        <v>624</v>
+        <v>561</v>
       </c>
       <c r="F25" t="n">
-        <v>1191</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="26">
@@ -989,13 +989,13 @@
         <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E26" t="n">
-        <v>380</v>
+        <v>451</v>
       </c>
       <c r="F26" t="n">
-        <v>1392</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="27">
@@ -1008,16 +1008,16 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E27" t="n">
-        <v>583</v>
+        <v>666</v>
       </c>
       <c r="F27" t="n">
-        <v>1260</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="28">
@@ -1030,16 +1030,16 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D28" t="n">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="E28" t="n">
-        <v>628</v>
+        <v>707</v>
       </c>
       <c r="F28" t="n">
-        <v>1810</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="29">
@@ -1052,16 +1052,16 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D29" t="n">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="E29" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F29" t="n">
-        <v>1225</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="30">
@@ -1074,16 +1074,16 @@
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D30" t="n">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="E30" t="n">
-        <v>515</v>
+        <v>579</v>
       </c>
       <c r="F30" t="n">
-        <v>1565</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="31">
@@ -1096,16 +1096,16 @@
         <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D31" t="n">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="E31" t="n">
-        <v>479</v>
+        <v>583</v>
       </c>
       <c r="F31" t="n">
-        <v>1108</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="32">
@@ -1118,16 +1118,16 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D32" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="E32" t="n">
-        <v>437</v>
+        <v>499</v>
       </c>
       <c r="F32" t="n">
-        <v>971</v>
+        <v>981</v>
       </c>
     </row>
     <row r="33">
@@ -1140,16 +1140,16 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D33" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E33" t="n">
-        <v>409</v>
+        <v>481</v>
       </c>
       <c r="F33" t="n">
-        <v>1013</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="34">
@@ -1165,13 +1165,13 @@
         <v>15</v>
       </c>
       <c r="D34" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E34" t="n">
-        <v>472</v>
+        <v>531</v>
       </c>
       <c r="F34" t="n">
-        <v>1063</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="35">
@@ -1184,16 +1184,16 @@
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D35" t="n">
-        <v>216</v>
+        <v>167</v>
       </c>
       <c r="E35" t="n">
-        <v>597</v>
+        <v>652</v>
       </c>
       <c r="F35" t="n">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="36">
@@ -1206,16 +1206,16 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D36" t="n">
-        <v>221</v>
+        <v>180</v>
       </c>
       <c r="E36" t="n">
-        <v>501</v>
+        <v>534</v>
       </c>
       <c r="F36" t="n">
-        <v>1260</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="37">
@@ -1228,16 +1228,16 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D37" t="n">
-        <v>328</v>
+        <v>273</v>
       </c>
       <c r="E37" t="n">
-        <v>589</v>
+        <v>628</v>
       </c>
       <c r="F37" t="n">
-        <v>1760</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="38">
@@ -1247,19 +1247,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D38" t="n">
-        <v>166</v>
+        <v>211</v>
       </c>
       <c r="E38" t="n">
-        <v>670</v>
+        <v>623</v>
       </c>
       <c r="F38" t="n">
-        <v>3610</v>
+        <v>3618</v>
       </c>
     </row>
     <row r="39">
@@ -1275,13 +1275,13 @@
         <v>20</v>
       </c>
       <c r="D39" t="n">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="E39" t="n">
-        <v>631</v>
+        <v>602</v>
       </c>
       <c r="F39" t="n">
-        <v>5774</v>
+        <v>5788</v>
       </c>
     </row>
     <row r="40">
@@ -1294,16 +1294,16 @@
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D40" t="n">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="E40" t="n">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="F40" t="n">
-        <v>6864</v>
+        <v>6867</v>
       </c>
     </row>
     <row r="41">
@@ -1319,13 +1319,13 @@
         <v>32</v>
       </c>
       <c r="D41" t="n">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="E41" t="n">
-        <v>737</v>
+        <v>724</v>
       </c>
       <c r="F41" t="n">
-        <v>5739</v>
+        <v>5744</v>
       </c>
     </row>
     <row r="42">
@@ -1335,19 +1335,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D42" t="n">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E42" t="n">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="F42" t="n">
-        <v>4980</v>
+        <v>4984</v>
       </c>
     </row>
     <row r="43">
@@ -1363,13 +1363,13 @@
         <v>39</v>
       </c>
       <c r="D43" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E43" t="n">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="F43" t="n">
-        <v>6393</v>
+        <v>6395</v>
       </c>
     </row>
     <row r="44">
@@ -1385,13 +1385,13 @@
         <v>51</v>
       </c>
       <c r="D44" t="n">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="E44" t="n">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="F44" t="n">
-        <v>6165</v>
+        <v>6175</v>
       </c>
     </row>
     <row r="45">
@@ -1401,19 +1401,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C45" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D45" t="n">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E45" t="n">
-        <v>897</v>
+        <v>922</v>
       </c>
       <c r="F45" t="n">
-        <v>4589</v>
+        <v>4602</v>
       </c>
     </row>
     <row r="46">
@@ -1423,19 +1423,19 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D46" t="n">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="E46" t="n">
-        <v>891</v>
+        <v>917</v>
       </c>
       <c r="F46" t="n">
-        <v>4203</v>
+        <v>4211</v>
       </c>
     </row>
     <row r="47">
@@ -1451,13 +1451,13 @@
         <v>77</v>
       </c>
       <c r="D47" t="n">
-        <v>461</v>
+        <v>432</v>
       </c>
       <c r="E47" t="n">
-        <v>1072</v>
+        <v>1109</v>
       </c>
       <c r="F47" t="n">
-        <v>5017</v>
+        <v>5022</v>
       </c>
     </row>
     <row r="48">
@@ -1467,19 +1467,19 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D48" t="n">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="E48" t="n">
-        <v>813</v>
+        <v>824</v>
       </c>
       <c r="F48" t="n">
-        <v>6209</v>
+        <v>6212</v>
       </c>
     </row>
   </sheetData>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-10T11:04:50</t>
+          <t>2026-10-15T18:46:36</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>135,390</t>
+          <t>136,127</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>4,142</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.31 seconds</t>
+          <t>3.84 seconds</t>
         </is>
       </c>
     </row>

--- a/0-assets/raw_data/main/3b-age-grouping/age_generation_quarterly_statistics.xlsx
+++ b/0-assets/raw_data/main/3b-age-grouping/age_generation_quarterly_statistics.xlsx
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-15T18:46:36</t>
+          <t>2026-10-15T21:48:18</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.84 seconds</t>
+          <t>2.10 seconds</t>
         </is>
       </c>
     </row>

--- a/0-assets/raw_data/main/3b-age-grouping/age_generation_quarterly_statistics.xlsx
+++ b/0-assets/raw_data/main/3b-age-grouping/age_generation_quarterly_statistics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly counts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run info" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Quarterly counts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Run info" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -461,7 +461,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -483,7 +483,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -505,10 +505,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -527,10 +527,10 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -549,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -571,10 +571,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -593,10 +593,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -615,13 +615,13 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -640,10 +640,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>240</v>
+        <v>112</v>
       </c>
       <c r="F11" t="n">
-        <v>16</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12">
@@ -684,10 +684,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>449</v>
+        <v>217</v>
       </c>
       <c r="F12" t="n">
-        <v>48</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13">
@@ -703,13 +703,13 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>702</v>
+        <v>297</v>
       </c>
       <c r="F13" t="n">
-        <v>84</v>
+        <v>490</v>
       </c>
     </row>
     <row r="14">
@@ -728,10 +728,10 @@
         <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>808</v>
+        <v>411</v>
       </c>
       <c r="F14" t="n">
-        <v>196</v>
+        <v>593</v>
       </c>
     </row>
     <row r="15">
@@ -747,13 +747,13 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>973</v>
+        <v>519</v>
       </c>
       <c r="F15" t="n">
-        <v>260</v>
+        <v>715</v>
       </c>
     </row>
     <row r="16">
@@ -769,13 +769,13 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>2666</v>
+        <v>1315</v>
       </c>
       <c r="F16" t="n">
-        <v>957</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="17">
@@ -791,13 +791,13 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>4203</v>
+        <v>2103</v>
       </c>
       <c r="F17" t="n">
-        <v>1678</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="18">
@@ -813,13 +813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E18" t="n">
-        <v>3754</v>
+        <v>2226</v>
       </c>
       <c r="F18" t="n">
-        <v>1972</v>
+        <v>3505</v>
       </c>
     </row>
     <row r="19">
@@ -835,13 +835,13 @@
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E19" t="n">
-        <v>2630</v>
+        <v>1529</v>
       </c>
       <c r="F19" t="n">
-        <v>1950</v>
+        <v>3053</v>
       </c>
     </row>
     <row r="20">
@@ -860,10 +860,10 @@
         <v>40</v>
       </c>
       <c r="E20" t="n">
-        <v>2147</v>
+        <v>1098</v>
       </c>
       <c r="F20" t="n">
-        <v>2343</v>
+        <v>3392</v>
       </c>
     </row>
     <row r="21">
@@ -879,13 +879,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>1119</v>
+        <v>678</v>
       </c>
       <c r="F21" t="n">
-        <v>1552</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="22">
@@ -901,13 +901,13 @@
         <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E22" t="n">
-        <v>994</v>
+        <v>778</v>
       </c>
       <c r="F22" t="n">
-        <v>1730</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="23">
@@ -923,13 +923,13 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E23" t="n">
-        <v>765</v>
+        <v>598</v>
       </c>
       <c r="F23" t="n">
-        <v>1320</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="24">
@@ -945,13 +945,13 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E24" t="n">
-        <v>657</v>
+        <v>515</v>
       </c>
       <c r="F24" t="n">
-        <v>1397</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="25">
@@ -970,10 +970,10 @@
         <v>45</v>
       </c>
       <c r="E25" t="n">
-        <v>561</v>
+        <v>506</v>
       </c>
       <c r="F25" t="n">
-        <v>1264</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="26">
@@ -989,13 +989,13 @@
         <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E26" t="n">
-        <v>451</v>
+        <v>377</v>
       </c>
       <c r="F26" t="n">
-        <v>1322</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="27">
@@ -1011,13 +1011,13 @@
         <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E27" t="n">
-        <v>666</v>
+        <v>602</v>
       </c>
       <c r="F27" t="n">
-        <v>1208</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="28">
@@ -1036,10 +1036,10 @@
         <v>128</v>
       </c>
       <c r="E28" t="n">
-        <v>707</v>
+        <v>639</v>
       </c>
       <c r="F28" t="n">
-        <v>1800</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="29">
@@ -1058,10 +1058,10 @@
         <v>160</v>
       </c>
       <c r="E29" t="n">
-        <v>524</v>
+        <v>507</v>
       </c>
       <c r="F29" t="n">
-        <v>1268</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="30">
@@ -1080,10 +1080,10 @@
         <v>127</v>
       </c>
       <c r="E30" t="n">
-        <v>579</v>
+        <v>561</v>
       </c>
       <c r="F30" t="n">
-        <v>1547</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="31">
@@ -1102,10 +1102,10 @@
         <v>116</v>
       </c>
       <c r="E31" t="n">
-        <v>583</v>
+        <v>557</v>
       </c>
       <c r="F31" t="n">
-        <v>1089</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="32">
@@ -1121,13 +1121,13 @@
         <v>22</v>
       </c>
       <c r="D32" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E32" t="n">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="F32" t="n">
-        <v>981</v>
+        <v>992</v>
       </c>
     </row>
     <row r="33">
@@ -1146,10 +1146,10 @@
         <v>137</v>
       </c>
       <c r="E33" t="n">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="F33" t="n">
-        <v>1016</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="34">
@@ -1168,10 +1168,10 @@
         <v>125</v>
       </c>
       <c r="E34" t="n">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="F34" t="n">
-        <v>1052</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="35">
@@ -1190,10 +1190,10 @@
         <v>167</v>
       </c>
       <c r="E35" t="n">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="F35" t="n">
-        <v>775</v>
+        <v>785</v>
       </c>
     </row>
     <row r="36">
@@ -1212,10 +1212,10 @@
         <v>180</v>
       </c>
       <c r="E36" t="n">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F36" t="n">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="37">
@@ -1275,13 +1275,13 @@
         <v>20</v>
       </c>
       <c r="D39" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E39" t="n">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F39" t="n">
-        <v>5788</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="40">
@@ -1297,7 +1297,7 @@
         <v>26</v>
       </c>
       <c r="D40" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E40" t="n">
         <v>578</v>
@@ -1319,13 +1319,13 @@
         <v>32</v>
       </c>
       <c r="D41" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E41" t="n">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F41" t="n">
-        <v>5744</v>
+        <v>5745</v>
       </c>
     </row>
     <row r="42">
@@ -1341,7 +1341,7 @@
         <v>31</v>
       </c>
       <c r="D42" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E42" t="n">
         <v>709</v>
@@ -1360,10 +1360,10 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D43" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="E43" t="n">
         <v>809</v>
@@ -1382,10 +1382,10 @@
         <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D44" t="n">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="E44" t="n">
         <v>946</v>
@@ -1404,10 +1404,10 @@
         <v>3</v>
       </c>
       <c r="C45" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="E45" t="n">
         <v>922</v>
@@ -1426,10 +1426,10 @@
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D46" t="n">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="E46" t="n">
         <v>917</v>
@@ -1448,10 +1448,10 @@
         <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D47" t="n">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="E47" t="n">
         <v>1109</v>
@@ -1473,7 +1473,7 @@
         <v>64</v>
       </c>
       <c r="D48" t="n">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="E48" t="n">
         <v>824</v>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-15T21:48:18</t>
+          <t>2026-10-17T22:04:46</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>136,127</t>
+          <t>136,160</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4,142</t>
+          <t>72</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.10 seconds</t>
+          <t>1.39 seconds</t>
         </is>
       </c>
     </row>
